--- a/IPPU/A2_Structure_Lists.xlsx
+++ b/IPPU/A2_Structure_Lists.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
   <si>
     <t>Year</t>
   </si>
@@ -244,16 +244,10 @@
     <t>E5IPPUPARAFFIN</t>
   </si>
   <si>
-    <t>CO2e_leakage</t>
-  </si>
-  <si>
     <t>CO2e_HFC</t>
   </si>
   <si>
     <t>CO2e_CEM</t>
-  </si>
-  <si>
-    <t>CO2e_consumption_com</t>
   </si>
   <si>
     <t>CO2e_IPPU</t>
@@ -663,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -704,9 +698,6 @@
       <c r="D5" t="s">
         <v>49</v>
       </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
@@ -717,9 +708,6 @@
       </c>
       <c r="D6" t="s">
         <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1253,13 +1241,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{672368E4-7DA2-4F46-8092-12990E476B43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4DB1239-CD56-4242-B9E8-139484FD69BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75A9F22B-3886-49BA-BB1B-2EC942F85793}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC225C2F-2725-480A-8E35-9214C61CA5AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44523AD-4D32-4870-9491-78560FC15FAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64AB2A7B-5764-41F7-995F-FAD1A0A8D50D}"/>
 </file>